--- a/GWD Data/WTP.xlsx
+++ b/GWD Data/WTP.xlsx
@@ -29,7 +29,7 @@
     <t>(i)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (14" Dia 65" Height) Weight – 21 kg, Tank Volume - 150 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
+    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (14" Dia 65" Height) Weight - 21 kg, Tank Volume - 150 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
   </si>
   <si>
     <t>FRP-1465 vessel (MR)</t>
@@ -77,7 +77,7 @@
     <t>(ii)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (16" Dia 65" Height) Weight – 22 kg, Tank Volume - 185 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
+    <t xml:space="preserve">Supplying, assembling, fibre reinforced polymer vessel (FRP) size  (16" Dia 65" Height) Weight - 22 kg, Tank Volume - 185 liter, Material- Polyethylene, Max Pressure -150 PSI, Max Vacuum- 5" Hg, Max temperature-49'c, Capacity- 1000-10000 L, opening at top &amp; bottom  including hire &amp; labour charges, fittings &amp; accessories etc.complete, as per direction of Engineer-in-charge </t>
   </si>
   <si>
     <t>FRP-1665 vessel (MR)</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">II.  MPV- (Multi port valve)    </t>
   </si>
   <si>
-    <t>Supplying, assembling, manually operated multi port valve 40 NB Material -PVC, Max pressure – 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+    <t>Supplying, assembling, manually operated multi port valve 40 NB Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
     <t>MPV-40 NB  (MR)</t>
@@ -146,13 +146,13 @@
     <t>LS</t>
   </si>
   <si>
-    <t>Supplying, assembling, manually operated multi port valve flower type 50NB Material -PVC, Max pressure – 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+    <t>Supplying, assembling, manually operated multi port valve flower type 50NB Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
     <t>MPV-50 NB  (MR)</t>
   </si>
   <si>
-    <t>Supplying, assembling, multi port valve 65 NB Manually Material -PVC, Max pressure – 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
+    <t>Supplying, assembling, multi port valve 65 NB Manually Material -PVC, Max pressure - 4kg/cm2,   including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge including hire &amp; labour charges, fittings &amp; accessories etc. all complete, as per direction of Engineer-in-charge</t>
   </si>
   <si>
     <t>MPV-65 NB (MR)</t>
@@ -888,6 +888,7 @@
       <sheetName val="GWD DR Abstract"/>
       <sheetName val="GWD MR Abstract"/>
       <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
@@ -963,6 +964,7 @@
       <sheetData sheetId="35"/>
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1264,7 +1266,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E60DC2B-1897-4121-A183-BD8298BAB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05B5533-7847-43C5-AAE3-F35D64B4B9A6}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/WTP.xlsx
+++ b/GWD Data/WTP.xlsx
@@ -911,6 +911,7 @@
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
       <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
       <sheetName val="PVC wo Trench"/>
       <sheetName val="PVC With Trench"/>
@@ -965,6 +966,7 @@
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1266,7 +1268,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05B5533-7847-43C5-AAE3-F35D64B4B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2910B234-8157-4F93-B70A-8057F2B0B9A6}">
   <dimension ref="A1:G465"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
